--- a/artfynd/A 36263-2026 artfynd.xlsx
+++ b/artfynd/A 36263-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135888158</v>
       </c>
       <c r="B2" t="n">
-        <v>98159</v>
+        <v>98170</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36263-2026 artfynd.xlsx
+++ b/artfynd/A 36263-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135888158</v>
       </c>
       <c r="B2" t="n">
-        <v>98170</v>
+        <v>98183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36263-2026 artfynd.xlsx
+++ b/artfynd/A 36263-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135888158</v>
       </c>
       <c r="B2" t="n">
-        <v>98183</v>
+        <v>98184</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36263-2026 artfynd.xlsx
+++ b/artfynd/A 36263-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135888158</v>
       </c>
       <c r="B2" t="n">
-        <v>98184</v>
+        <v>98197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36263-2026 artfynd.xlsx
+++ b/artfynd/A 36263-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135888158</v>
       </c>
       <c r="B2" t="n">
-        <v>98197</v>
+        <v>98198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
